--- a/ScheduleFinalFull.xlsx
+++ b/ScheduleFinalFull.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\BadgerOffice\Prep\Timesheets\Timesheet_Exports_2026-06-18\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\BadgerOffice\Prep\Timesheets\Timesheet_Exports_2026-06-22\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5B17E38-0065-4AB2-A7B0-919C89B643C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F133147F-92EE-4211-93AE-20B14F38F601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2690" windowWidth="14400" windowHeight="8250" tabRatio="150" xr2:uid="{77AAEA21-1A26-436C-8AA0-2999EADC84A9}"/>
+    <workbookView xWindow="0" yWindow="2690" windowWidth="14400" windowHeight="8250" tabRatio="150" xr2:uid="{8A10BE84-9037-46ED-8F78-5BDD61C3EFBD}"/>
   </bookViews>
   <sheets>
     <sheet name="ScheduleFinalFull" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="645">
   <si>
     <t>ScheduleDateOfInv</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>(815) 273-3575</t>
+  </si>
+  <si>
+    <t>LIGHTERS, ROLLING PAPERS, TOBACCO 4' ALL NEED TO BE COUNTED UNDER THE TOBACCO CATEGORY</t>
   </si>
   <si>
     <t>1/16/2026 8:35:15 PM</t>
@@ -2407,7 +2410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D41B86C-E870-45F0-A2A9-284B4E4D8143}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995336B3-394B-41AF-B955-1DB462663FE6}">
   <dimension ref="A1:AH66"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2776,7 +2779,7 @@
         <v>76</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>43</v>
@@ -2806,7 +2809,7 @@
         <v>65</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U4" s="3" t="s">
         <v>51</v>
@@ -2827,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB4" s="3" t="s">
         <v>68</v>
@@ -2868,19 +2871,19 @@
         <v>37</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>43</v>
@@ -2889,7 +2892,7 @@
         <v>43</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>61</v>
@@ -2898,19 +2901,19 @@
         <v>0</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>51</v>
@@ -2931,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>53</v>
@@ -2943,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG5" s="7" t="b">
         <v>0</v>
@@ -2960,28 +2963,28 @@
         <v>46174</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>42</v>
@@ -2990,7 +2993,7 @@
         <v>43</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>45</v>
@@ -3002,22 +3005,22 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V6" s="7" t="b">
         <v>0</v>
@@ -3035,22 +3038,22 @@
         <v>0</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC6" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD6" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE6" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG6" s="7" t="b">
         <v>0</v>
@@ -3064,28 +3067,28 @@
         <v>46174</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>42</v>
@@ -3106,22 +3109,22 @@
         <v>0</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V7" s="7" t="b">
         <v>0</v>
@@ -3139,22 +3142,22 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD7" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG7" s="7" t="b">
         <v>0</v>
@@ -3168,7 +3171,7 @@
         <v>46174</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>35</v>
@@ -3177,19 +3180,19 @@
         <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>42</v>
@@ -3201,28 +3204,28 @@
         <v>43</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O8" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>51</v>
@@ -3243,10 +3246,10 @@
         <v>0</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>43</v>
@@ -3255,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG8" s="7" t="b">
         <v>0</v>
@@ -3278,22 +3281,22 @@
         <v>35</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>42</v>
@@ -3305,31 +3308,31 @@
         <v>43</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O9" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V9" s="7" t="b">
         <v>0</v>
@@ -3347,10 +3350,10 @@
         <v>0</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>43</v>
@@ -3359,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG9" s="7" t="b">
         <v>0</v>
@@ -3379,7 +3382,7 @@
         <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>36</v>
@@ -3388,49 +3391,49 @@
         <v>37</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>43</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O10" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>51</v>
@@ -3451,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>53</v>
@@ -3483,7 +3486,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>36</v>
@@ -3492,16 +3495,16 @@
         <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>42</v>
@@ -3513,7 +3516,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>61</v>
@@ -3522,19 +3525,19 @@
         <v>0</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U11" s="3" t="s">
         <v>51</v>
@@ -3555,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AB11" s="3" t="s">
         <v>53</v>
@@ -3584,7 +3587,7 @@
         <v>46175</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>35</v>
@@ -3593,19 +3596,19 @@
         <v>36</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>42</v>
@@ -3617,28 +3620,28 @@
         <v>43</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>51</v>
@@ -3659,22 +3662,22 @@
         <v>0</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC12" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD12" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE12" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG12" s="7" t="b">
         <v>0</v>
@@ -3688,7 +3691,7 @@
         <v>46175</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>35</v>
@@ -3697,19 +3700,19 @@
         <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>42</v>
@@ -3721,28 +3724,28 @@
         <v>43</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O13" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U13" s="3" t="s">
         <v>51</v>
@@ -3763,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC13" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD13" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG13" s="7" t="b">
         <v>0</v>
@@ -3795,58 +3798,58 @@
         <v>34</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>43</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O14" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>51</v>
@@ -3867,10 +3870,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>43</v>
@@ -3879,10 +3882,10 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG14" s="7" t="b">
         <v>0</v>
@@ -3908,22 +3911,22 @@
         <v>37</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>43</v>
@@ -3938,19 +3941,19 @@
         <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>51</v>
@@ -3971,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>68</v>
@@ -4000,28 +4003,28 @@
         <v>46176</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>42</v>
@@ -4033,31 +4036,31 @@
         <v>43</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O16" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V16" s="7" t="b">
         <v>0</v>
@@ -4075,10 +4078,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AB16" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>43</v>
@@ -4087,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="AE16" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF16" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG16" s="7" t="b">
         <v>0</v>
@@ -4104,28 +4107,28 @@
         <v>46176</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>42</v>
@@ -4137,31 +4140,31 @@
         <v>43</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O17" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V17" s="7" t="b">
         <v>0</v>
@@ -4179,22 +4182,22 @@
         <v>0</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AB17" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC17" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD17" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE17" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AF17" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG17" s="7" t="b">
         <v>0</v>
@@ -4208,28 +4211,28 @@
         <v>46176</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>42</v>
@@ -4241,31 +4244,31 @@
         <v>43</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O18" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V18" s="7" t="b">
         <v>0</v>
@@ -4283,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AB18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AC18" s="6" t="s">
         <v>43</v>
@@ -4295,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="AE18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AF18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG18" s="7" t="b">
         <v>0</v>
@@ -4312,7 +4315,7 @@
         <v>46176</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>35</v>
@@ -4321,19 +4324,19 @@
         <v>36</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>42</v>
@@ -4345,28 +4348,28 @@
         <v>43</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O19" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U19" s="3" t="s">
         <v>51</v>
@@ -4387,22 +4390,22 @@
         <v>0</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AB19" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC19" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD19" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE19" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF19" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG19" s="7" t="b">
         <v>0</v>
@@ -4416,7 +4419,7 @@
         <v>46176</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>35</v>
@@ -4425,19 +4428,19 @@
         <v>36</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>42</v>
@@ -4449,28 +4452,28 @@
         <v>43</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O20" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>51</v>
@@ -4491,22 +4494,22 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC20" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD20" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE20" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF20" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG20" s="7" t="b">
         <v>0</v>
@@ -4520,28 +4523,28 @@
         <v>46176</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>42</v>
@@ -4553,28 +4556,28 @@
         <v>43</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O21" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>51</v>
@@ -4595,22 +4598,22 @@
         <v>0</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AB21" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC21" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD21" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE21" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG21" s="7" t="b">
         <v>0</v>
@@ -4624,28 +4627,28 @@
         <v>46176</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>42</v>
@@ -4657,28 +4660,28 @@
         <v>43</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O22" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T22" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>51</v>
@@ -4699,22 +4702,22 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AB22" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC22" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD22" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE22" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF22" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG22" s="7" t="b">
         <v>0</v>
@@ -4740,19 +4743,19 @@
         <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>43</v>
@@ -4761,28 +4764,28 @@
         <v>43</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O23" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>51</v>
@@ -4803,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>53</v>
@@ -4835,28 +4838,28 @@
         <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>43</v>
@@ -4865,28 +4868,28 @@
         <v>43</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O24" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T24" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>51</v>
@@ -4907,10 +4910,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AB24" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>43</v>
@@ -4919,10 +4922,10 @@
         <v>0</v>
       </c>
       <c r="AE24" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF24" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG24" s="7" t="b">
         <v>0</v>
@@ -4936,28 +4939,28 @@
         <v>46177</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>42</v>
@@ -4969,31 +4972,31 @@
         <v>43</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O25" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V25" s="7" t="b">
         <v>0</v>
@@ -5011,10 +5014,10 @@
         <v>0</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AB25" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>43</v>
@@ -5023,10 +5026,10 @@
         <v>0</v>
       </c>
       <c r="AE25" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AF25" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG25" s="7" t="b">
         <v>0</v>
@@ -5040,28 +5043,28 @@
         <v>46177</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>42</v>
@@ -5073,31 +5076,31 @@
         <v>43</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O26" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V26" s="7" t="b">
         <v>0</v>
@@ -5115,22 +5118,22 @@
         <v>0</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AB26" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC26" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD26" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE26" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AF26" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG26" s="7" t="b">
         <v>0</v>
@@ -5144,28 +5147,28 @@
         <v>46177</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>42</v>
@@ -5177,31 +5180,31 @@
         <v>43</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O27" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V27" s="7" t="b">
         <v>0</v>
@@ -5219,22 +5222,22 @@
         <v>0</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AB27" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC27" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD27" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE27" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AF27" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG27" s="7" t="b">
         <v>0</v>
@@ -5248,28 +5251,28 @@
         <v>46177</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>42</v>
@@ -5281,31 +5284,31 @@
         <v>43</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O28" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T28" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V28" s="7" t="b">
         <v>0</v>
@@ -5323,10 +5326,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AB28" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>43</v>
@@ -5335,10 +5338,10 @@
         <v>0</v>
       </c>
       <c r="AE28" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AF28" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG28" s="7" t="b">
         <v>0</v>
@@ -5364,49 +5367,49 @@
         <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>43</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O29" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>51</v>
@@ -5427,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>53</v>
@@ -5468,19 +5471,19 @@
         <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>43</v>
@@ -5489,28 +5492,28 @@
         <v>43</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O30" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q30" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T30" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U30" s="3" t="s">
         <v>51</v>
@@ -5531,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AB30" s="3" t="s">
         <v>53</v>
@@ -5569,22 +5572,22 @@
         <v>36</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>43</v>
@@ -5593,28 +5596,28 @@
         <v>43</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O31" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U31" s="3" t="s">
         <v>51</v>
@@ -5635,10 +5638,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AB31" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>43</v>
@@ -5647,10 +5650,10 @@
         <v>0</v>
       </c>
       <c r="AE31" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AF31" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG31" s="7" t="b">
         <v>0</v>
@@ -5670,28 +5673,28 @@
         <v>35</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>43</v>
@@ -5706,22 +5709,22 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T32" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V32" s="7" t="b">
         <v>0</v>
@@ -5739,22 +5742,22 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AB32" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC32" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD32" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE32" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF32" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG32" s="7" t="b">
         <v>0</v>
@@ -5768,7 +5771,7 @@
         <v>46178</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>35</v>
@@ -5780,16 +5783,16 @@
         <v>37</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>42</v>
@@ -5801,28 +5804,28 @@
         <v>43</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O33" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T33" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>51</v>
@@ -5843,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="AA33" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>53</v>
@@ -5855,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AE33" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AF33" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG33" s="7" t="b">
         <v>0</v>
@@ -5884,22 +5887,22 @@
         <v>37</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>43</v>
@@ -5908,25 +5911,25 @@
         <v>60</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O34" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T34" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U34" s="3" t="s">
         <v>51</v>
@@ -5947,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AB34" s="3" t="s">
         <v>53</v>
@@ -5959,10 +5962,10 @@
         <v>0</v>
       </c>
       <c r="AE34" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AF34" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG34" s="7" t="b">
         <v>0</v>
@@ -5982,22 +5985,22 @@
         <v>35</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>42</v>
@@ -6018,22 +6021,22 @@
         <v>0</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T35" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V35" s="7" t="b">
         <v>0</v>
@@ -6051,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="AA35" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>53</v>
@@ -6063,10 +6066,10 @@
         <v>0</v>
       </c>
       <c r="AE35" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AF35" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG35" s="7" t="b">
         <v>0</v>
@@ -6080,7 +6083,7 @@
         <v>46181</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>35</v>
@@ -6089,19 +6092,19 @@
         <v>36</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>42</v>
@@ -6113,28 +6116,28 @@
         <v>43</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O36" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="S36" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T36" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U36" s="3" t="s">
         <v>51</v>
@@ -6155,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="AA36" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AB36" s="3" t="s">
         <v>53</v>
@@ -6167,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AE36" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AF36" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG36" s="7" t="b">
         <v>0</v>
@@ -6184,7 +6187,7 @@
         <v>46181</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>35</v>
@@ -6196,16 +6199,16 @@
         <v>37</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>42</v>
@@ -6217,28 +6220,28 @@
         <v>43</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O37" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T37" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="U37" s="3" t="s">
         <v>51</v>
@@ -6259,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="AA37" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AB37" s="3" t="s">
         <v>68</v>
@@ -6271,10 +6274,10 @@
         <v>0</v>
       </c>
       <c r="AE37" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AF37" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG37" s="7" t="b">
         <v>0</v>
@@ -6288,28 +6291,28 @@
         <v>46181</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>42</v>
@@ -6321,31 +6324,31 @@
         <v>43</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O38" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T38" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V38" s="7" t="b">
         <v>0</v>
@@ -6363,10 +6366,10 @@
         <v>0</v>
       </c>
       <c r="AA38" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AB38" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>43</v>
@@ -6375,10 +6378,10 @@
         <v>0</v>
       </c>
       <c r="AE38" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AF38" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG38" s="7" t="b">
         <v>0</v>
@@ -6392,28 +6395,28 @@
         <v>46181</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>42</v>
@@ -6425,31 +6428,31 @@
         <v>43</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O39" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="S39" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T39" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V39" s="7" t="b">
         <v>0</v>
@@ -6467,10 +6470,10 @@
         <v>0</v>
       </c>
       <c r="AA39" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AB39" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>43</v>
@@ -6479,10 +6482,10 @@
         <v>0</v>
       </c>
       <c r="AE39" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AF39" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG39" s="7" t="b">
         <v>0</v>
@@ -6508,16 +6511,16 @@
         <v>37</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>42</v>
@@ -6538,19 +6541,19 @@
         <v>0</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="S40" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T40" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>51</v>
@@ -6571,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="AA40" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AB40" s="3" t="s">
         <v>53</v>
@@ -6600,7 +6603,7 @@
         <v>46182</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>35</v>
@@ -6609,19 +6612,19 @@
         <v>36</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>42</v>
@@ -6642,19 +6645,19 @@
         <v>0</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T41" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>51</v>
@@ -6675,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AA41" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>53</v>
@@ -6687,10 +6690,10 @@
         <v>0</v>
       </c>
       <c r="AE41" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AF41" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG41" s="7" t="b">
         <v>0</v>
@@ -6707,28 +6710,28 @@
         <v>34</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>43</v>
@@ -6737,28 +6740,28 @@
         <v>43</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O42" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T42" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>51</v>
@@ -6779,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AB42" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>43</v>
@@ -6791,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF42" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG42" s="7" t="b">
         <v>0</v>
@@ -6808,7 +6811,7 @@
         <v>46182</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>35</v>
@@ -6817,19 +6820,19 @@
         <v>36</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>42</v>
@@ -6841,28 +6844,28 @@
         <v>43</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T43" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>51</v>
@@ -6883,22 +6886,22 @@
         <v>0</v>
       </c>
       <c r="AA43" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AB43" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC43" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD43" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE43" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF43" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG43" s="7" t="b">
         <v>0</v>
@@ -6915,28 +6918,28 @@
         <v>34</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>43</v>
@@ -6945,28 +6948,28 @@
         <v>43</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O44" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T44" s="8" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>51</v>
@@ -6987,10 +6990,10 @@
         <v>0</v>
       </c>
       <c r="AA44" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AB44" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>43</v>
@@ -6999,10 +7002,10 @@
         <v>0</v>
       </c>
       <c r="AE44" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG44" s="7" t="b">
         <v>0</v>
@@ -7022,22 +7025,22 @@
         <v>35</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>42</v>
@@ -7058,22 +7061,22 @@
         <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T45" s="8" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V45" s="7" t="b">
         <v>0</v>
@@ -7091,22 +7094,22 @@
         <v>0</v>
       </c>
       <c r="AA45" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AB45" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC45" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD45" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE45" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF45" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG45" s="7" t="b">
         <v>0</v>
@@ -7126,22 +7129,22 @@
         <v>35</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>42</v>
@@ -7162,22 +7165,22 @@
         <v>0</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T46" s="8" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V46" s="7" t="b">
         <v>0</v>
@@ -7195,22 +7198,22 @@
         <v>0</v>
       </c>
       <c r="AA46" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AB46" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC46" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD46" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE46" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF46" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG46" s="7" t="b">
         <v>0</v>
@@ -7224,28 +7227,28 @@
         <v>46183</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>42</v>
@@ -7257,31 +7260,31 @@
         <v>43</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O47" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T47" s="8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V47" s="7" t="b">
         <v>0</v>
@@ -7299,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="AA47" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AB47" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>43</v>
@@ -7311,10 +7314,10 @@
         <v>0</v>
       </c>
       <c r="AE47" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG47" s="7" t="b">
         <v>0</v>
@@ -7328,28 +7331,28 @@
         <v>46183</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>42</v>
@@ -7361,28 +7364,28 @@
         <v>43</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O48" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T48" s="8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>51</v>
@@ -7403,22 +7406,22 @@
         <v>0</v>
       </c>
       <c r="AA48" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AB48" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD48" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE48" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF48" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG48" s="7" t="b">
         <v>0</v>
@@ -7438,25 +7441,25 @@
         <v>35</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>43</v>
@@ -7465,7 +7468,7 @@
         <v>43</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>43</v>
@@ -7474,22 +7477,22 @@
         <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T49" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V49" s="7" t="b">
         <v>0</v>
@@ -7507,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="AA49" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>53</v>
@@ -7519,10 +7522,10 @@
         <v>0</v>
       </c>
       <c r="AE49" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AF49" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG49" s="7" t="b">
         <v>0</v>
@@ -7548,28 +7551,28 @@
         <v>37</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>43</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>61</v>
@@ -7578,19 +7581,19 @@
         <v>0</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T50" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="U50" s="3" t="s">
         <v>51</v>
@@ -7611,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="AA50" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AB50" s="3" t="s">
         <v>53</v>
@@ -7643,7 +7646,7 @@
         <v>34</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>36</v>
@@ -7652,28 +7655,28 @@
         <v>37</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>43</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>43</v>
@@ -7682,19 +7685,19 @@
         <v>0</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="S51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T51" s="8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>51</v>
@@ -7715,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="AA51" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AB51" s="3" t="s">
         <v>53</v>
@@ -7747,25 +7750,25 @@
         <v>34</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>42</v>
@@ -7777,28 +7780,28 @@
         <v>43</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O52" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T52" s="8" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>51</v>
@@ -7819,10 +7822,10 @@
         <v>0</v>
       </c>
       <c r="AA52" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AB52" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>43</v>
@@ -7831,10 +7834,10 @@
         <v>0</v>
       </c>
       <c r="AE52" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF52" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG52" s="7" t="b">
         <v>0</v>
@@ -7854,22 +7857,22 @@
         <v>35</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>42</v>
@@ -7881,7 +7884,7 @@
         <v>43</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>61</v>
@@ -7890,22 +7893,22 @@
         <v>0</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="S53" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T53" s="8" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V53" s="7" t="b">
         <v>0</v>
@@ -7923,7 +7926,7 @@
         <v>0</v>
       </c>
       <c r="AA53" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AB53" s="3" t="s">
         <v>53</v>
@@ -7935,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE53" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AF53" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG53" s="7" t="b">
         <v>0</v>
@@ -7961,22 +7964,22 @@
         <v>36</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>43</v>
@@ -7985,28 +7988,28 @@
         <v>43</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O54" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T54" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>51</v>
@@ -8027,10 +8030,10 @@
         <v>0</v>
       </c>
       <c r="AA54" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AB54" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>43</v>
@@ -8039,10 +8042,10 @@
         <v>0</v>
       </c>
       <c r="AE54" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AF54" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG54" s="7" t="b">
         <v>0</v>
@@ -8056,28 +8059,28 @@
         <v>46185</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>42</v>
@@ -8098,22 +8101,22 @@
         <v>0</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="S55" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T55" s="8" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V55" s="7" t="b">
         <v>0</v>
@@ -8131,22 +8134,22 @@
         <v>0</v>
       </c>
       <c r="AA55" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AB55" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC55" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD55" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE55" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF55" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG55" s="7" t="b">
         <v>0</v>
@@ -8166,28 +8169,28 @@
         <v>35</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>43</v>
@@ -8202,22 +8205,22 @@
         <v>0</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T56" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V56" s="7" t="b">
         <v>0</v>
@@ -8235,22 +8238,22 @@
         <v>0</v>
       </c>
       <c r="AA56" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AB56" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC56" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD56" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE56" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF56" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG56" s="7" t="b">
         <v>0</v>
@@ -8264,28 +8267,28 @@
         <v>46185</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>42</v>
@@ -8297,31 +8300,31 @@
         <v>43</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O57" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T57" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V57" s="7" t="b">
         <v>0</v>
@@ -8339,22 +8342,22 @@
         <v>0</v>
       </c>
       <c r="AA57" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AB57" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC57" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD57" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE57" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AF57" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG57" s="7" t="b">
         <v>0</v>
@@ -8368,7 +8371,7 @@
         <v>46185</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>35</v>
@@ -8377,19 +8380,19 @@
         <v>36</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>42</v>
@@ -8401,28 +8404,28 @@
         <v>43</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O58" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T58" s="8" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>51</v>
@@ -8443,22 +8446,22 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AB58" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC58" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD58" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE58" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF58" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG58" s="7" t="b">
         <v>0</v>
@@ -8478,25 +8481,25 @@
         <v>35</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>43</v>
@@ -8505,7 +8508,7 @@
         <v>43</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>61</v>
@@ -8514,22 +8517,22 @@
         <v>0</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T59" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V59" s="7" t="b">
         <v>0</v>
@@ -8547,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="AA59" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>53</v>
@@ -8559,10 +8562,10 @@
         <v>0</v>
       </c>
       <c r="AE59" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AF59" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG59" s="7" t="b">
         <v>0</v>
@@ -8588,16 +8591,16 @@
         <v>37</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>42</v>
@@ -8612,25 +8615,25 @@
         <v>60</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O60" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>49</v>
       </c>
       <c r="T60" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>51</v>
@@ -8651,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="AA60" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AB60" s="3" t="s">
         <v>53</v>
@@ -8663,10 +8666,10 @@
         <v>0</v>
       </c>
       <c r="AE60" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AF60" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG60" s="7" t="b">
         <v>0</v>
@@ -8680,7 +8683,7 @@
         <v>46188</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>35</v>
@@ -8692,13 +8695,13 @@
         <v>37</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>76</v>
@@ -8713,28 +8716,28 @@
         <v>43</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O61" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="S61" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T61" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="U61" s="3" t="s">
         <v>51</v>
@@ -8755,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AB61" s="3" t="s">
         <v>68</v>
@@ -8790,28 +8793,28 @@
         <v>35</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>43</v>
@@ -8826,22 +8829,22 @@
         <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T62" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V62" s="7" t="b">
         <v>0</v>
@@ -8859,22 +8862,22 @@
         <v>0</v>
       </c>
       <c r="AA62" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AB62" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC62" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD62" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE62" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF62" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG62" s="7" t="b">
         <v>0</v>
@@ -8894,22 +8897,22 @@
         <v>35</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>42</v>
@@ -8930,22 +8933,22 @@
         <v>0</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T63" s="8" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V63" s="7" t="b">
         <v>0</v>
@@ -8963,22 +8966,22 @@
         <v>0</v>
       </c>
       <c r="AA63" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AB63" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC63" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AD63" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE63" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AF63" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG63" s="7" t="b">
         <v>0</v>
@@ -8992,28 +8995,28 @@
         <v>46188</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>42</v>
@@ -9025,31 +9028,31 @@
         <v>43</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O64" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T64" s="8" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V64" s="7" t="b">
         <v>0</v>
@@ -9067,10 +9070,10 @@
         <v>0</v>
       </c>
       <c r="AA64" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AB64" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC64" s="6" t="s">
         <v>43</v>
@@ -9079,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="AE64" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AF64" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG64" s="7" t="b">
         <v>0</v>
@@ -9096,28 +9099,28 @@
         <v>46188</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>42</v>
@@ -9129,31 +9132,31 @@
         <v>43</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O65" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>63</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="S65" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T65" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="V65" s="7" t="b">
         <v>0</v>
@@ -9171,10 +9174,10 @@
         <v>0</v>
       </c>
       <c r="AA65" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AB65" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AC65" s="6" t="s">
         <v>43</v>
@@ -9183,10 +9186,10 @@
         <v>0</v>
       </c>
       <c r="AE65" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AF65" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG65" s="7" t="b">
         <v>0</v>
@@ -9200,28 +9203,28 @@
         <v>46188</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>42</v>
@@ -9233,28 +9236,28 @@
         <v>43</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O66" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>47</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T66" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>51</v>
@@ -9275,22 +9278,22 @@
         <v>0</v>
       </c>
       <c r="AA66" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AB66" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC66" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD66" s="7" t="b">
         <v>1</v>
       </c>
       <c r="AE66" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AF66" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG66" s="7" t="b">
         <v>0</v>
@@ -9301,71 +9304,71 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" xr:uid="{5F4A8297-0BE3-4492-96DF-4105AF181708}"/>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{09F25837-82A4-4CAA-B3CF-CFEAF4F6CE9E}"/>
-    <hyperlink ref="H4" r:id="rId2" xr:uid="{6F073FBF-AC4D-4AD3-A79E-D0AC65439474}"/>
-    <hyperlink ref="H5" xr:uid="{63B486CE-F981-4A4A-83A8-698D487A25C0}"/>
-    <hyperlink ref="H6" r:id="rId3" xr:uid="{0300EDFB-094F-4C8A-AF31-C42099E7E731}"/>
-    <hyperlink ref="H7" r:id="rId4" xr:uid="{7E3A40F7-D942-4F5E-8D69-1164292C3024}"/>
-    <hyperlink ref="H8" r:id="rId5" xr:uid="{1854E614-C586-4B49-8352-D26C39FE8339}"/>
-    <hyperlink ref="H9" r:id="rId6" xr:uid="{171693CD-D556-41D2-AC0B-DBB729A59FC8}"/>
-    <hyperlink ref="H10" xr:uid="{5C16184B-89CD-49CF-973A-5AA3400728E4}"/>
-    <hyperlink ref="H11" xr:uid="{AEC4464D-35DA-4058-849E-F1F504571970}"/>
-    <hyperlink ref="H12" r:id="rId7" xr:uid="{8887AE29-133A-4809-9051-7D6391D1DDF3}"/>
-    <hyperlink ref="H13" r:id="rId8" xr:uid="{8905D3B5-5227-405C-A600-5291CECFB7E7}"/>
-    <hyperlink ref="H14" xr:uid="{3CDF86A6-6391-4936-A77D-6C457C366231}"/>
-    <hyperlink ref="H15" r:id="rId9" xr:uid="{F6E507FD-5EA5-4E24-BD20-D16E855FBD3E}"/>
-    <hyperlink ref="H16" r:id="rId10" xr:uid="{20CF3067-AF38-4BA3-A81D-3A3DE2D37B64}"/>
-    <hyperlink ref="H17" r:id="rId11" xr:uid="{62A535A7-19B9-441D-B861-8265ED9BAD6A}"/>
-    <hyperlink ref="H18" r:id="rId12" xr:uid="{FEC94CE7-839F-4615-86A9-5BCC631C843E}"/>
-    <hyperlink ref="H19" r:id="rId13" xr:uid="{8300287A-77DD-4233-82F7-209DF5364800}"/>
-    <hyperlink ref="H20" r:id="rId14" xr:uid="{74738855-C860-4D8C-BA1C-FEB3921E3110}"/>
-    <hyperlink ref="H21" r:id="rId15" xr:uid="{7AD124E8-473C-446F-B299-58523F4B34B9}"/>
-    <hyperlink ref="H22" r:id="rId16" xr:uid="{7D0B7A29-29F7-4FB5-B5BC-B3C00F734248}"/>
-    <hyperlink ref="H23" r:id="rId17" xr:uid="{FC17ED53-889C-46B3-B5A7-C7CB14D4C10F}"/>
-    <hyperlink ref="H24" xr:uid="{66E51AB7-CB47-48CB-BA54-D35C9E16DD49}"/>
-    <hyperlink ref="H25" r:id="rId18" xr:uid="{0FCDAC16-74F4-4532-AA92-BE4B2F06D1FE}"/>
-    <hyperlink ref="H26" r:id="rId19" xr:uid="{28AFF472-B2EF-4505-840E-51800E106B2F}"/>
-    <hyperlink ref="H27" r:id="rId20" xr:uid="{3F866D36-C1C3-408D-8EA1-A6D501F0D4E6}"/>
-    <hyperlink ref="H28" r:id="rId21" xr:uid="{159165EB-C9F6-4FD5-A967-E29984F01C0D}"/>
-    <hyperlink ref="H29" r:id="rId22" xr:uid="{96603BF5-97DF-4A71-8D04-B9B5C3FD643B}"/>
-    <hyperlink ref="H30" r:id="rId23" xr:uid="{037D140C-1EF2-4B71-99CD-4E1C6920196E}"/>
-    <hyperlink ref="H31" xr:uid="{973DAC63-727B-4467-9C99-473408B7B597}"/>
-    <hyperlink ref="H32" r:id="rId24" xr:uid="{03218D3A-8147-45E0-89E9-703B543B912E}"/>
-    <hyperlink ref="H33" r:id="rId25" xr:uid="{AD509291-58A0-492F-8F6C-BA020083DF0C}"/>
-    <hyperlink ref="H34" xr:uid="{FCDD2C8B-D3CC-4FDF-83C2-1141C9C4BCB9}"/>
-    <hyperlink ref="H35" r:id="rId26" xr:uid="{43719AB7-BA1B-4870-8817-2F7F601A6357}"/>
-    <hyperlink ref="H36" r:id="rId27" xr:uid="{4D7D50CB-9825-4DD6-AD7D-87BCFBAAA224}"/>
-    <hyperlink ref="H37" r:id="rId28" xr:uid="{57A11B22-F859-4313-AE6F-A50D4C9B816A}"/>
-    <hyperlink ref="H38" r:id="rId29" xr:uid="{81C9F95E-1A51-442E-96DB-ED9BD722299A}"/>
-    <hyperlink ref="H39" r:id="rId30" xr:uid="{B702C4C0-9DDC-4DD0-98BE-8E370B984E77}"/>
-    <hyperlink ref="H40" xr:uid="{3D89BC6D-5861-49C2-B7C6-D6091AD2D698}"/>
-    <hyperlink ref="H41" r:id="rId31" xr:uid="{225CE778-4AF1-4478-81EC-C311F19BB62C}"/>
-    <hyperlink ref="H42" xr:uid="{5F21F091-CA36-477B-BB4D-A3FD70583356}"/>
-    <hyperlink ref="H43" r:id="rId32" xr:uid="{8980D408-5493-4395-AE8F-6669B6E15D5C}"/>
-    <hyperlink ref="H44" r:id="rId33" xr:uid="{EA11987C-0B95-43D7-A7C0-9101EC0A1082}"/>
-    <hyperlink ref="H45" r:id="rId34" xr:uid="{C1A9FB50-4EC5-4347-BA76-644D01FD2472}"/>
-    <hyperlink ref="H46" r:id="rId35" xr:uid="{C87C4854-1242-4559-8AED-B5659771DF88}"/>
-    <hyperlink ref="H47" r:id="rId36" xr:uid="{59AC141E-AED9-41CB-99B9-714938958E17}"/>
-    <hyperlink ref="H48" r:id="rId37" xr:uid="{77352606-C19F-4D8F-BFFA-41F3FEEDBECE}"/>
-    <hyperlink ref="H49" r:id="rId38" xr:uid="{A0B488F1-68BB-4A6E-A2A2-0988CA0EB91A}"/>
-    <hyperlink ref="H50" xr:uid="{F7DC5E28-7F6A-4D27-9C8D-040A0354BA36}"/>
-    <hyperlink ref="H51" r:id="rId39" xr:uid="{C5D99A96-E2B9-425F-916B-8416CD55FF08}"/>
-    <hyperlink ref="H52" xr:uid="{7133B41C-F1BB-4FF3-A163-8F016EBFF7A6}"/>
-    <hyperlink ref="H53" r:id="rId40" xr:uid="{34B8EDFA-F305-4E44-A75B-BD23E1D85C5A}"/>
-    <hyperlink ref="H54" xr:uid="{5916ED65-F9C6-4619-BB85-C621DA9FC091}"/>
-    <hyperlink ref="H55" r:id="rId41" xr:uid="{68DBA820-21C0-4EE6-AEA6-0EDCE318333D}"/>
-    <hyperlink ref="H56" r:id="rId42" xr:uid="{E6C3414B-8CBD-4065-A544-E96240E9E5FC}"/>
-    <hyperlink ref="H57" r:id="rId43" xr:uid="{024813D5-BD6E-4B2A-AA8F-321E672A1D2C}"/>
-    <hyperlink ref="H58" r:id="rId44" xr:uid="{B25CC7EE-4B77-472B-B195-DE470404A8DE}"/>
-    <hyperlink ref="H59" r:id="rId45" xr:uid="{67F0C0A7-6CA6-4D2A-ACB7-161C8162E5F2}"/>
-    <hyperlink ref="H60" xr:uid="{C04427AA-95CA-465C-81DC-EB56415DF82C}"/>
-    <hyperlink ref="H61" r:id="rId46" xr:uid="{BF724FBA-03AF-4029-8183-94DD8F4CE748}"/>
-    <hyperlink ref="H62" r:id="rId47" xr:uid="{4D9660C3-E131-4B31-8DCC-7FCD05ADE27E}"/>
-    <hyperlink ref="H63" r:id="rId48" xr:uid="{9742368B-4A2D-466C-B26A-84C94FDC0779}"/>
-    <hyperlink ref="H64" r:id="rId49" xr:uid="{016A9BDF-A4FA-4254-B49C-CCED439798B6}"/>
-    <hyperlink ref="H65" r:id="rId50" xr:uid="{B2AFA9A9-8605-4C04-B540-19C5EDAC0638}"/>
-    <hyperlink ref="H66" r:id="rId51" xr:uid="{7002CCF8-79B7-460B-99E7-CBA83ED72C50}"/>
+    <hyperlink ref="H2" xr:uid="{279278E1-1DCC-4484-9637-00AAAC3DFC9F}"/>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{21EBC0C6-AE3A-4898-B2AA-82319270974B}"/>
+    <hyperlink ref="H4" r:id="rId2" xr:uid="{1A634497-DB0C-46F6-B666-40EA89890523}"/>
+    <hyperlink ref="H5" xr:uid="{9F5F493C-82EB-479A-94E8-2F10AB361537}"/>
+    <hyperlink ref="H6" r:id="rId3" xr:uid="{4D3B9FB3-DD05-4125-ABF1-25EEEBA00265}"/>
+    <hyperlink ref="H7" r:id="rId4" xr:uid="{5D1E6C8B-3AB0-4E22-A6B7-6F2FA0209813}"/>
+    <hyperlink ref="H8" r:id="rId5" xr:uid="{7EF2032F-994C-4025-AD00-599C0611C5A2}"/>
+    <hyperlink ref="H9" r:id="rId6" xr:uid="{31F1FD45-4658-40E1-8EE2-C439B19F2355}"/>
+    <hyperlink ref="H10" xr:uid="{1B1509D6-AAAE-4BBA-B7D7-943A981FD7CB}"/>
+    <hyperlink ref="H11" xr:uid="{C85335E1-A767-4AB3-8756-7173238E70BF}"/>
+    <hyperlink ref="H12" r:id="rId7" xr:uid="{9C8AAB01-0100-477F-94E4-314D69FD6E1C}"/>
+    <hyperlink ref="H13" r:id="rId8" xr:uid="{3152C34D-2A32-498B-BBA8-594ABE4CE638}"/>
+    <hyperlink ref="H14" xr:uid="{45356E1B-820E-435E-B31C-DA38FA71C1CD}"/>
+    <hyperlink ref="H15" r:id="rId9" xr:uid="{9BB8E473-9B08-4A35-9655-9AFC1313354B}"/>
+    <hyperlink ref="H16" r:id="rId10" xr:uid="{60C47A74-B155-4BBE-B638-D67C322D6C40}"/>
+    <hyperlink ref="H17" r:id="rId11" xr:uid="{2187647E-F04C-479B-9908-D67AD32B3D42}"/>
+    <hyperlink ref="H18" r:id="rId12" xr:uid="{2FF5B655-DF52-4C30-8D69-CE7749AB5E65}"/>
+    <hyperlink ref="H19" r:id="rId13" xr:uid="{449A1220-228A-4101-8C92-2B5F60AF475B}"/>
+    <hyperlink ref="H20" r:id="rId14" xr:uid="{0D798E1F-2181-4835-8962-672FA7C127CD}"/>
+    <hyperlink ref="H21" r:id="rId15" xr:uid="{07ECAE53-B1B7-40F6-B114-C7E70C97AEBD}"/>
+    <hyperlink ref="H22" r:id="rId16" xr:uid="{A2ADE16B-E823-4C48-A671-722DCD423534}"/>
+    <hyperlink ref="H23" r:id="rId17" xr:uid="{ABA66C5E-47EF-472D-A085-5735AB1BF588}"/>
+    <hyperlink ref="H24" xr:uid="{74BA2B7C-74B1-40C7-A548-57623D7E5185}"/>
+    <hyperlink ref="H25" r:id="rId18" xr:uid="{844C45A0-4A9E-47F1-AC97-A2DB1FCE14CC}"/>
+    <hyperlink ref="H26" r:id="rId19" xr:uid="{895B513A-4CFC-4DDC-AD44-53871B44CD2C}"/>
+    <hyperlink ref="H27" r:id="rId20" xr:uid="{0D6F60F2-FD7A-4321-9E43-0948C2B35063}"/>
+    <hyperlink ref="H28" r:id="rId21" xr:uid="{C8D53750-B8CD-4158-9884-6C4BEAD56A37}"/>
+    <hyperlink ref="H29" r:id="rId22" xr:uid="{8F4FA60E-800D-4B3D-A688-9381502288E2}"/>
+    <hyperlink ref="H30" r:id="rId23" xr:uid="{2090F8DD-305E-46D6-B65B-16DB3B3CADE9}"/>
+    <hyperlink ref="H31" xr:uid="{FD644C94-2491-44DE-BC91-7B275C6D58BE}"/>
+    <hyperlink ref="H32" r:id="rId24" xr:uid="{AF9BE5C3-005C-4E53-BE83-B4E2814A2371}"/>
+    <hyperlink ref="H33" r:id="rId25" xr:uid="{4DE1DEE0-CE03-4689-B303-528D9E119E85}"/>
+    <hyperlink ref="H34" xr:uid="{A1D535E5-2913-49B9-B2C6-09C2FC0242EC}"/>
+    <hyperlink ref="H35" r:id="rId26" xr:uid="{4E6FB9CB-BAF7-4B1D-90AB-B73655D8BE33}"/>
+    <hyperlink ref="H36" r:id="rId27" xr:uid="{9C5C5E3A-21C0-4CED-9AD8-20AC7A755D63}"/>
+    <hyperlink ref="H37" r:id="rId28" xr:uid="{46F2C851-FB18-4271-BA33-B0B9798CE27B}"/>
+    <hyperlink ref="H38" r:id="rId29" xr:uid="{C14212A0-5D3E-4EBE-8D86-8C4EA956F264}"/>
+    <hyperlink ref="H39" r:id="rId30" xr:uid="{F30575ED-7579-4A70-B287-B2DCD9F77679}"/>
+    <hyperlink ref="H40" xr:uid="{C0563BDE-570B-4FA3-A1B1-EC09A32F82C3}"/>
+    <hyperlink ref="H41" r:id="rId31" xr:uid="{274503F4-8B73-415C-AF17-F925DB4ADE54}"/>
+    <hyperlink ref="H42" xr:uid="{60A5C328-69BC-4515-BB2D-471C06518E90}"/>
+    <hyperlink ref="H43" r:id="rId32" xr:uid="{DDE95FBB-2BDE-45CF-8D88-DB1B6487DD39}"/>
+    <hyperlink ref="H44" r:id="rId33" xr:uid="{649487F4-1BBB-4388-B223-68D89B546424}"/>
+    <hyperlink ref="H45" r:id="rId34" xr:uid="{1371A711-CCE3-4DB4-87D5-637A1256916D}"/>
+    <hyperlink ref="H46" r:id="rId35" xr:uid="{8E2451AC-7603-40C3-8E77-75A47E062059}"/>
+    <hyperlink ref="H47" r:id="rId36" xr:uid="{BD3BEA2E-FF1C-4DD7-AA3C-9F66CD36D448}"/>
+    <hyperlink ref="H48" r:id="rId37" xr:uid="{593DD5BA-F466-471F-BC6A-0CD50E3AB0F6}"/>
+    <hyperlink ref="H49" r:id="rId38" xr:uid="{347F1021-9161-4EE7-B16E-C5F12E20B0A5}"/>
+    <hyperlink ref="H50" xr:uid="{F8FA667F-232A-4000-B600-922E694A8E47}"/>
+    <hyperlink ref="H51" r:id="rId39" xr:uid="{05B379D2-D77C-4A83-8B92-AE40AD1C0DCE}"/>
+    <hyperlink ref="H52" xr:uid="{7206C489-9F82-457A-ADCE-A2BDAD4D3B0C}"/>
+    <hyperlink ref="H53" r:id="rId40" xr:uid="{2903A009-CDF1-420C-B2AB-6760E38BA337}"/>
+    <hyperlink ref="H54" xr:uid="{50A8D247-806D-4A16-B0C5-81D7F83B74E1}"/>
+    <hyperlink ref="H55" r:id="rId41" xr:uid="{5B28E149-A481-4E30-9412-B2C82BDB9594}"/>
+    <hyperlink ref="H56" r:id="rId42" xr:uid="{5FA3C606-6B25-4A3A-BDD5-AE99B5D59524}"/>
+    <hyperlink ref="H57" r:id="rId43" xr:uid="{CC74C871-C105-41CB-A4D2-8B0FA431EDC2}"/>
+    <hyperlink ref="H58" r:id="rId44" xr:uid="{7803BECA-E474-4BE1-8941-B2BC6E969F47}"/>
+    <hyperlink ref="H59" r:id="rId45" xr:uid="{3A41B084-38C1-4315-AEDB-E0AD215C8128}"/>
+    <hyperlink ref="H60" xr:uid="{72DB42C6-9332-4181-A4FF-30106DB05393}"/>
+    <hyperlink ref="H61" r:id="rId46" xr:uid="{FA39D0EE-F095-418A-A7EB-7D9B22470C7F}"/>
+    <hyperlink ref="H62" r:id="rId47" xr:uid="{C7311530-6A45-4E13-9649-B802EDA0BE11}"/>
+    <hyperlink ref="H63" r:id="rId48" xr:uid="{E41C8898-0096-4A84-8EEE-74141F143113}"/>
+    <hyperlink ref="H64" r:id="rId49" xr:uid="{9A8E1983-E8D1-4886-ACFE-101E31639ABD}"/>
+    <hyperlink ref="H65" r:id="rId50" xr:uid="{E2D10608-93FB-4203-8FA6-0A952AE5739B}"/>
+    <hyperlink ref="H66" r:id="rId51" xr:uid="{E10D4618-FB37-43CB-A76A-B3D9C2254083}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
